--- a/events/Pau_2015_WC/Pau_2015_WC_start.xlsx
+++ b/events/Pau_2015_WC/Pau_2015_WC_start.xlsx
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J117" t="n">

--- a/events/Pau_2015_WC/Pau_2015_WC_start.xlsx
+++ b/events/Pau_2015_WC/Pau_2015_WC_start.xlsx
@@ -1733,6 +1733,11 @@
           <t>MERJAN Richard</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>45918</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7133,6 +7138,11 @@
       <c r="R117" t="inlineStr">
         <is>
           <t>MERJAN Richard</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>45918</t>
         </is>
       </c>
     </row>
